--- a/AtchisonRegime/Outputs/China/df_regLTRates_China.xlsx
+++ b/AtchisonRegime/Outputs/China/df_regLTRates_China.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3076,6 +3076,32 @@
         <v>0</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B102" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2.426363888888889</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.4055898365539715</v>
+      </c>
+      <c r="F102" t="b">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-1.963471017062621</v>
+      </c>
+      <c r="H102" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
